--- a/Selenium/nykaa_end_to_end/test_data/data.xlsx
+++ b/Selenium/nykaa_end_to_end/test_data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9598ef7ed350fd67/Documents/Yoga_5370346_WiproCapstone/Selenium/nykaa_end_to_end/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{28F531A5-0CD4-42AB-9789-D32F7E0F529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB524AEA-EC38-4E4F-9DA8-59B66E401B4C}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{28F531A5-0CD4-42AB-9789-D32F7E0F529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7248216-80B3-44FE-9DF8-7442C2684858}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{D404606D-13B5-4A31-A046-6C92B6895290}"/>
   </bookViews>
@@ -34,19 +34,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>phone</t>
+  </si>
+  <si>
+    <t>pincode</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>yogalakshmin24@gmail.com</t>
+  </si>
+  <si>
+    <t>Yoga</t>
+  </si>
+  <si>
+    <t>Tamil Nadu</t>
+  </si>
+  <si>
+    <t>Coimbatore</t>
+  </si>
+  <si>
+    <t>flatno</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>Selvapuram</t>
+  </si>
+  <si>
+    <t>cardno</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>cvv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -69,13 +122,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -392,23 +448,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E4F6E3-00B8-4192-9F42-5788BDF012AB}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>6369887216</v>
       </c>
+      <c r="B2">
+        <v>641026</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>391</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>5678923</v>
+      </c>
+      <c r="J2">
+        <v>1229</v>
+      </c>
+      <c r="K2">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{BF273800-269B-48A9-8603-8756A84A2189}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Selenium/nykaa_end_to_end/test_data/data.xlsx
+++ b/Selenium/nykaa_end_to_end/test_data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9598ef7ed350fd67/Documents/Yoga_5370346_WiproCapstone/Selenium/nykaa_end_to_end/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{28F531A5-0CD4-42AB-9789-D32F7E0F529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7248216-80B3-44FE-9DF8-7442C2684858}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{28F531A5-0CD4-42AB-9789-D32F7E0F529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B7D8ED-F78E-4597-9074-AE2432631044}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{D404606D-13B5-4A31-A046-6C92B6895290}"/>
+    <workbookView minimized="1" xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{D404606D-13B5-4A31-A046-6C92B6895290}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
